--- a/evac_by_zip/evac_by_zip_2026-09-15.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-09-15.xlsx
@@ -663,7 +663,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>97021</t>
+          <t>97023</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -689,64 +689,64 @@
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
+          <t>Austin</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>225</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>231</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
           <t>Grasshopper</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>97023</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Austin</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>225</v>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>231</v>
+        <v>3</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Hood River</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -782,10 +782,10 @@
         <v>225</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E9" s="11" t="n">
         <v>264</v>
@@ -801,10 +801,10 @@
         <v>137</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E10" s="13" t="n">
         <v>169</v>
@@ -820,10 +820,10 @@
         <v>362</v>
       </c>
       <c r="C11" s="15" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E11" s="15" t="n">
         <v>433</v>
@@ -938,22 +938,22 @@
     <row r="4">
       <c r="A4" s="18" t="inlineStr">
         <is>
-          <t>97021</t>
+          <t>97023</t>
         </is>
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>NF 27</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="E4" s="18" t="inlineStr">
@@ -963,32 +963,32 @@
       </c>
       <c r="F4" s="18" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G4" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>97023</t>
+          <t>97886</t>
         </is>
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>US-OR-UNI-UCO-140618N</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Union</t>
         </is>
       </c>
       <c r="E5" s="18" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="F5" s="18" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G5" s="18" t="n">
@@ -1008,22 +1008,22 @@
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>97886</t>
+          <t>97358</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-140618N</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>Union</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="E6" s="18" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="F6" s="18" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G6" s="18" t="n">
@@ -1041,143 +1041,143 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>97063</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>NF 27</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Elk Mountain</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>1</v>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>97358</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>1</v>
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>Mill Creek Buttes</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>97041</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>Elk Mountain</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Cooper Spur North</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Hood River</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>4</v>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>158</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>97041</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>Mill Creek Buttes</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Cooper Spur South</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>Hood River</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>2</v>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="11">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>Cooper Spur North</t>
+          <t>Gibson Prairie</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -1208,11 +1208,11 @@
       </c>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="G11" s="22" t="n">
-        <v>158</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>Cooper Spur South</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -1243,80 +1243,80 @@
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="G12" s="22" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>Gibson Prairie</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>NF 27</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>4</v>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>97063</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>NF 27</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="G14" s="22" t="n">
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="n">
         <v>1</v>
       </c>
     </row>
